--- a/src/files/archivo_actualizado.xlsx
+++ b/src/files/archivo_actualizado.xlsx
@@ -17,15 +17,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
-  <si>
-    <t>NOMBRE DEL EMPLEADO: AGUILAR BRAVO JAQUELINE MONTSERRAT</t>
-  </si>
-  <si>
-    <t>CÉDULA: 11056</t>
-  </si>
-  <si>
-    <t>CARGO: Operario de Aseo</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+  <si>
+    <t>NOMBRE DEL EMPLEADO: FERNANDEZ CANELA CLAUDIA</t>
+  </si>
+  <si>
+    <t>CÉDULA: 10003</t>
+  </si>
+  <si>
+    <t>CARGO: Operador de Empaque</t>
   </si>
   <si>
     <t>ÁREA: Producción</t>
@@ -46,25 +46,28 @@
     <t>FIRMA</t>
   </si>
   <si>
-    <t>RESPIRADOR</t>
-  </si>
-  <si>
-    <t>2025-11-10</t>
+    <t>GUANTES NEGROS</t>
+  </si>
+  <si>
+    <t>2025-12-04</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>BOTA DE SEGURIDAD</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>BOTA DE SEGURIDAD</t>
-  </si>
-  <si>
-    <t>2026-04-15</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>El Sr. (a) AGUILAR BRAVO JAQUELINE MONTSERRAT identificado con cédula de ciudadanía No: 11056, manifiesto que estoy informado de los riesgos contra los que me protegen estos elementos que estoy recibiendo, de las actividades u ocasiones en que debo utilizarlos, de la forma correcta para su uso y sus limitaciones. Me comprometo a hacer buen uso de los EPP entregados, a su vez conozco y acpeto ser  responsable por la pérdida y daños ocasionados por el mal uso o descuido, de ser así autorizo a la empresa para que haga el descuento de mi salario, prestaciones sociales y demás emolumentos laborales, del costo de los EPP. De igual forma para efectos de control de la dotación, devolveré la anteriormente entregada al momento de recibir la del siguiente período. La no utilización de los elementos de protección personal y el descuido de los mismos acarrea sanciones administrativas y/o disciplinarias.</t>
+    <t>El Sr. (a) FERNANDEZ CANELA CLAUDIA identificado con cédula de ciudadanía No: 10003, manifiesto que estoy informado de los riesgos contra los que me protegen estos elementos que estoy recibiendo, de las actividades u ocasiones en que debo utilizarlos, de la forma correcta para su uso y sus limitaciones. Me comprometo a hacer buen uso de los EPP entregados, a su vez conozco y acpeto ser  responsable por la pérdida y daños ocasionados por el mal uso o descuido, de ser así autorizo a la empresa para que haga el descuento de mi salario, prestaciones sociales y demás emolumentos laborales, del costo de los EPP. De igual forma para efectos de control de la dotación, devolveré la anteriormente entregada al momento de recibir la del siguiente período. La no utilización de los elementos de protección personal y el descuido de los mismos acarrea sanciones administrativas y/o disciplinarias.</t>
   </si>
 </sst>
 </file>
@@ -944,7 +947,7 @@
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F10" s="6"/>
     </row>
@@ -957,7 +960,7 @@
     </row>
     <row r="12" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -966,7 +969,7 @@
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -1003,7 +1006,7 @@
     </row>
     <row r="18" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1012,7 +1015,7 @@
     </row>
     <row r="19" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
@@ -1021,7 +1024,7 @@
     </row>
     <row r="20" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
@@ -1030,7 +1033,7 @@
     </row>
     <row r="21" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -1046,7 +1049,7 @@
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
@@ -1055,7 +1058,7 @@
     </row>
     <row r="24" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
@@ -1064,7 +1067,7 @@
     </row>
     <row r="25" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
@@ -1080,7 +1083,7 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -1089,7 +1092,7 @@
     </row>
     <row r="28" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="6"/>
@@ -1098,7 +1101,7 @@
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
@@ -1107,7 +1110,7 @@
     </row>
     <row r="30" ht="20.1" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="6"/>
@@ -1137,7 +1140,7 @@
     </row>
     <row r="34" ht="36.75" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
